--- a/data/trans_camb/IP1014-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Clase-trans_camb.xlsx
@@ -641,17 +641,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,11</t>
+          <t>-2,78; 1,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,0</t>
+          <t>-5,51; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,12</t>
+          <t>-1,34; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-4,08; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,47</t>
+          <t>-1,48; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,21</t>
+          <t>-0,42; 2,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,04</t>
+          <t>-0,5; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,0</t>
+          <t>-1,16; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,95</t>
+          <t>-1,21; 1,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,85</t>
+          <t>-1,3; 2,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,72</t>
+          <t>-0,6; 1,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,94</t>
+          <t>-0,77; 0,91</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,53</t>
+          <t>-0,2; 0,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,0</t>
+          <t>-0,55; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,86</t>
+          <t>-0,44; 0,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,13</t>
+          <t>-0,89; 0,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,49</t>
+          <t>-0,25; 0,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,03</t>
+          <t>-0,51; 0,03</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 429,62</t>
+          <t>-67,82; 474,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 271,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,89; 300,68</t>
+          <t>-58,35; 342,38</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,22</t>
+          <t>-100,0; 82,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Clase-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,94</t>
+          <t>-2,79; 1,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,0</t>
+          <t>-4,8; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,01</t>
+          <t>-1,34; 1,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,0</t>
+          <t>-2,36; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,0</t>
+          <t>-3,72; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>-3,44; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,47</t>
+          <t>-1,36; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,26</t>
+          <t>-0,39; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,03</t>
+          <t>-0,42; 0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,0</t>
+          <t>-1,17; 0,0</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,95</t>
+          <t>-1,17; 1,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,08</t>
+          <t>-1,22; 1,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,66</t>
+          <t>-0,44; 1,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,91</t>
+          <t>-0,69; 1,13</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,59</t>
+          <t>-0,2; 0,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,0</t>
+          <t>-0,57; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,81</t>
+          <t>-0,46; 0,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,13</t>
+          <t>-1,0; 0,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,5</t>
+          <t>-0,22; 0,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,03</t>
+          <t>-0,57; -0,01</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 474,2</t>
+          <t>-64,86; 496,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 271,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 342,38</t>
+          <t>-55,68; 382,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,41</t>
+          <t>-100,0; 74,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,79; 2,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,16; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,33</t>
+          <t>-1,34; 1,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,0</t>
+          <t>-2,35; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-36,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-36,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,0</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,47</t>
+          <t>-1,79; 0,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>-0,34; 2,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,16</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,98</t>
+          <t>-0,51; 1,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,0</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>225,18%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>225,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>-1,19; 1,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,23; 1,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,96</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,69</t>
+          <t>-0,37; 1,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,13</t>
+          <t>-0,76; 0,94</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>61,55%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>61,55%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,1</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,5</t>
+          <t>-0,49; 0,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,0</t>
+          <t>-0,94; 0,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,85</t>
+          <t>-0,2; 0,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,08</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,52</t>
+          <t>-0,29; 0,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; -0,01</t>
+          <t>-0,52; 0,03</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>32,42%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-63,68%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>97,68%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-63,68%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,0; 429,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,86; 496,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 382,24</t>
+          <t>-60,89; 300,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,47</t>
+          <t>-100,0; 77,22</t>
         </is>
       </c>
     </row>
